--- a/request_forms/027_documentary_sound_mixing_request_form--request_forms.xlsx
+++ b/request_forms/027_documentary_sound_mixing_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mike'}</t>
+          <t>mike</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mike'}</t>
+          <t>Mike</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sally'}</t>
+          <t>sally</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sally'}</t>
+          <t>Sally</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tv_show'}</t>
+          <t>tv_show</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'TV Show'}</t>
+          <t>TV Show</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'stereo'}</t>
+          <t>stereo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Stereo'}</t>
+          <t>Stereo</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mono'}</t>
+          <t>mono</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mono'}</t>
+          <t>Mono</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'surround_sound'}</t>
+          <t>surround_sound</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Surround Sound'}</t>
+          <t>Surround Sound</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in_review'}</t>
+          <t>in_review</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In Review'}</t>
+          <t>In Review</t>
         </is>
       </c>
     </row>
